--- a/web/public/2027학년도_수시모집_전국대학_경쟁률취합_정보분석3팀_최신.xlsx
+++ b/web/public/2027학년도_수시모집_전국대학_경쟁률취합_정보분석3팀_최신.xlsx
@@ -574,7 +574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>수집 일시: 2026-09-17 17:03:24 | 작성: 정보분석3팀 | 대상: 총 12개 대학</t>
+          <t>수집 일시: 2026-09-17 17:16:42 | 작성: 정보분석3팀 | 대상: 총 12개 대학</t>
         </is>
       </c>
     </row>
